--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487636_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487636_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.194</v>
+        <v>12.2297</v>
       </c>
       <c r="E2" t="n">
-        <v>12.7416</v>
+        <v>11.9408</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4524</v>
+        <v>0.2889</v>
       </c>
       <c r="G2" t="n">
         <v>9.664300000000001</v>
@@ -610,13 +610,13 @@
         <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5879</v>
+        <v>0.6236</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2146</v>
+        <v>0.4138</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3733</v>
+        <v>0.2098</v>
       </c>
       <c r="V2" t="n">
         <v>1.5537</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8067</v>
+        <v>6.1342</v>
       </c>
       <c r="E3" t="n">
-        <v>6.34</v>
+        <v>6.6403</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5334</v>
+        <v>-0.5061</v>
       </c>
       <c r="G3" t="n">
         <v>3.8961</v>
@@ -688,13 +688,13 @@
         <v>0.7761</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4192</v>
+        <v>-0.0917</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5451</v>
+        <v>-0.2448</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1259</v>
+        <v>0.1531</v>
       </c>
       <c r="V3" t="n">
         <v>1.5537</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9036</v>
+        <v>5.4953</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7892</v>
+        <v>5.4899</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1145</v>
+        <v>0.0054</v>
       </c>
       <c r="G4" t="n">
         <v>3.8965</v>
@@ -766,13 +766,13 @@
         <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3407</v>
+        <v>0.251</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5451</v>
+        <v>0.1556</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2044</v>
+        <v>0.0954</v>
       </c>
       <c r="V4" t="n">
         <v>0.3776</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7395</v>
+        <v>1.9476</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7166</v>
+        <v>3.4153</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.977</v>
+        <v>-1.4676</v>
       </c>
       <c r="G5" t="n">
         <v>0.6673</v>
@@ -844,13 +844,13 @@
         <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7887</v>
+        <v>0.9968</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7608</v>
+        <v>0.4595</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0279</v>
+        <v>0.5373</v>
       </c>
       <c r="V5" t="n">
         <v>1.8358</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9622000000000001</v>
+        <v>1.5895</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5216</v>
+        <v>1.8219</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5594</v>
+        <v>-0.2324</v>
       </c>
       <c r="G6" t="n">
         <v>1.6163</v>
@@ -922,13 +922,13 @@
         <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8004</v>
+        <v>-0.173</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7874</v>
+        <v>-0.4871</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.013</v>
+        <v>0.3141</v>
       </c>
       <c r="V6" t="n">
         <v>-0.0478</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4178</v>
+        <v>0.6453</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2832</v>
+        <v>0.4834</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1346</v>
+        <v>0.1619</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0366</v>
@@ -1000,13 +1000,13 @@
         <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1276</v>
+        <v>0.0998</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1817</v>
+        <v>0.0185</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0541</v>
+        <v>0.0813</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4273</v>
+        <v>-0.1726</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6461</v>
+        <v>-0.4459</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2188</v>
+        <v>0.2733</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3301</v>
@@ -1078,13 +1078,13 @@
         <v>0.194</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2912</v>
+        <v>-0.0364</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0606</v>
+        <v>0.1396</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2306</v>
+        <v>-0.1761</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4587</v>
+        <v>-0.5954</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3509</v>
+        <v>2.0506</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8095</v>
+        <v>-2.646</v>
       </c>
       <c r="G9" t="n">
         <v>0.4559</v>
@@ -1156,13 +1156,13 @@
         <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08550000000000001</v>
+        <v>-0.0513</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2434</v>
+        <v>-0.0569</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1579</v>
+        <v>0.0056</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6119</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8933</v>
+        <v>-1.7303</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1177</v>
+        <v>-0.583</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.011</v>
+        <v>-1.1473</v>
       </c>
       <c r="G10" t="n">
         <v>0.2377</v>
@@ -1234,13 +1234,13 @@
         <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9645</v>
+        <v>0.1276</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8501</v>
+        <v>0.1494</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1144</v>
+        <v>-0.0219</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3194</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7937</v>
+        <v>-2.8477</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6412</v>
+        <v>-0.9405</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1525</v>
+        <v>-1.9072</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9141</v>
@@ -1312,13 +1312,13 @@
         <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8794999999999999</v>
+        <v>0.0665</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8479</v>
+        <v>-0.1472</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0316</v>
+        <v>0.2137</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0464</v>
+        <v>-4.7189</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2134</v>
+        <v>-3.9131</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.833</v>
+        <v>-0.8057</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5976</v>
@@ -1390,13 +1390,13 @@
         <v>0.7761</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2974</v>
+        <v>0.625</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0595</v>
+        <v>0.2408</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3569</v>
+        <v>0.3842</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6119</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.29</v>
+        <v>-5.8623</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.2732</v>
+        <v>-5.8728</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0167</v>
+        <v>0.0105</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7649</v>
@@ -1468,13 +1468,13 @@
         <v>0.7761</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1101</v>
+        <v>-0.6825</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6662</v>
+        <v>-0.2658</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4439</v>
+        <v>-0.4166</v>
       </c>
       <c r="V13" t="n">
         <v>0.6597</v>
@@ -1507,7 +1507,7 @@
         <v>20.0869</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.9722</v>
+        <v>-7.972299999999999</v>
       </c>
       <c r="G14" t="n">
         <v>12.7908</v>
@@ -1546,10 +1546,10 @@
         <v>9.701499999999998</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7553</v>
+        <v>1.7554</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3753999999999998</v>
+        <v>0.3754000000000001</v>
       </c>
       <c r="U14" t="n">
         <v>1.3799</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.252</v>
+        <v>2.6876</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3445</v>
+        <v>2.6438</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0925</v>
+        <v>0.0438</v>
       </c>
       <c r="G15" t="n">
         <v>0.1293</v>
@@ -1624,13 +1624,13 @@
         <v>2.1344</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7346</v>
+        <v>0.1702</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9724</v>
+        <v>0.2717</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2378</v>
+        <v>-0.1015</v>
       </c>
       <c r="V15" t="n">
         <v>1.2239</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5609</v>
+        <v>2.0609</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3115</v>
+        <v>1.1113</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2494</v>
+        <v>0.9496</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8269</v>
@@ -1702,13 +1702,13 @@
         <v>1.1642</v>
       </c>
       <c r="S16" t="n">
-        <v>0.952</v>
+        <v>0.452</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0595</v>
+        <v>-0.2597</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0115</v>
+        <v>0.7117</v>
       </c>
       <c r="V16" t="n">
         <v>1.2716</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8454</v>
+        <v>1.3642</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1921</v>
+        <v>0.7927</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6533</v>
+        <v>0.5715</v>
       </c>
       <c r="G17" t="n">
         <v>0.7745</v>
@@ -1780,13 +1780,13 @@
         <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7947</v>
+        <v>-0.2759</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8479</v>
+        <v>-0.2473</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0532</v>
+        <v>-0.0286</v>
       </c>
       <c r="V17" t="n">
         <v>1.8358</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3768</v>
+        <v>-0.6042</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2204</v>
+        <v>-0.4206</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1563</v>
+        <v>-0.1836</v>
       </c>
       <c r="G18" t="n">
         <v>-0.953</v>
@@ -1858,13 +1858,13 @@
         <v>0.194</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3822</v>
+        <v>0.1548</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3645</v>
+        <v>0.1643</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0177</v>
+        <v>-0.0095</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. BAILLO HERNÁNDEZ</t>
+          <t>P. VILLANUEVA LAZARO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4863</v>
+        <v>-1.5345</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7709</v>
+        <v>0.2089</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2572</v>
+        <v>-1.7434</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4547</v>
+        <v>-1.5846</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2663</v>
+        <v>-0.3205</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1884</v>
+        <v>-1.2641</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1612</v>
+        <v>2.5619</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2018</v>
+        <v>1.2399</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0406</v>
+        <v>1.3219</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2935</v>
+        <v>-4.1464</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0645</v>
+        <v>-1.5604</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.229</v>
+        <v>-2.586</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3582</v>
+        <v>2.1344</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2983</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3963</v>
+        <v>-0.3648</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.098</v>
+        <v>0.2686</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2821</v>
+        <v>-0.0478</v>
       </c>
       <c r="W19" t="n">
-        <v>1.506</v>
+        <v>-0.0478</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>B. BAILLO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4691</v>
+        <v>-1.6419</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1903</v>
+        <v>0.6698</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6594</v>
+        <v>-2.3117</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.1713</v>
+        <v>-2.4547</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6121</v>
+        <v>-1.2663</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.5592</v>
+        <v>-1.1884</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9603</v>
+        <v>-0.1612</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7343</v>
+        <v>-0.2018</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.774</v>
+        <v>0.0406</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.1316</v>
+        <v>-2.2935</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.3464</v>
+        <v>-1.0645</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7852</v>
+        <v>-1.229</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1344</v>
+        <v>0.3881</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1045</v>
+        <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.1427</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3061</v>
+        <v>0.2952</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2035</v>
+        <v>-0.1525</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9418</v>
+        <v>0.2821</v>
       </c>
       <c r="W20" t="n">
-        <v>0.894</v>
+        <v>1.506</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8358</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. VILLANUEVA LAZARO</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1346</v>
+        <v>-2.1877</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0914</v>
+        <v>0.6898</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0432</v>
+        <v>-2.8774</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5846</v>
+        <v>-3.1713</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3205</v>
+        <v>-0.6121</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2641</v>
+        <v>-2.5592</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5619</v>
+        <v>0.9603</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2399</v>
+        <v>1.7343</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3219</v>
+        <v>-0.774</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.1464</v>
+        <v>-4.1316</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5604</v>
+        <v>-2.3464</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.586</v>
+        <v>-1.7852</v>
       </c>
       <c r="P21" t="n">
-        <v>0.194</v>
+        <v>2.1344</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1344</v>
+        <v>3.1045</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6963</v>
+        <v>-0.2089</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6651</v>
+        <v>-0.1944</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0312</v>
+        <v>-0.0145</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0478</v>
+        <v>-0.9418</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0478</v>
+        <v>0.894</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8422</v>
+        <v>-2.9869</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2254</v>
+        <v>2.0262</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.0676</v>
+        <v>-5.0131</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2638</v>
@@ -2170,13 +2170,13 @@
         <v>2.5224</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2367</v>
+        <v>-0.3813</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2113</v>
+        <v>-0.4105</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0253</v>
+        <v>0.0292</v>
       </c>
       <c r="V22" t="n">
         <v>-0.894</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1864</v>
+        <v>-3.5585</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0089</v>
+        <v>-0.4083</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1775</v>
+        <v>-3.1502</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9675</v>
@@ -2248,13 +2248,13 @@
         <v>1.5523</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.607</v>
+        <v>-0.9791</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0296</v>
+        <v>-0.429</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5774</v>
+        <v>-0.5501</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2239</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.2775</v>
+        <v>-5.7136</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2582</v>
+        <v>0.6586</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.5358</v>
+        <v>-6.3722</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4727</v>
@@ -2326,13 +2326,13 @@
         <v>0.3881</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2974</v>
+        <v>-0.7335</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6057</v>
+        <v>-0.2053</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6918</v>
+        <v>-0.5282</v>
       </c>
       <c r="V24" t="n">
         <v>-4.8955</v>
@@ -2362,10 +2362,10 @@
         <v>-12.1146</v>
       </c>
       <c r="E25" t="n">
-        <v>7.972200000000001</v>
+        <v>7.9722</v>
       </c>
       <c r="F25" t="n">
-        <v>-20.0868</v>
+        <v>-20.0867</v>
       </c>
       <c r="G25" t="n">
         <v>-12.7907</v>
@@ -2395,7 +2395,7 @@
         <v>-10.9557</v>
       </c>
       <c r="P25" t="n">
-        <v>5.821</v>
+        <v>5.821000000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-9.701699999999999</v>
@@ -2404,13 +2404,13 @@
         <v>15.5227</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7554</v>
+        <v>-1.7552</v>
       </c>
       <c r="T25" t="n">
         <v>-1.3798</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3756</v>
+        <v>-0.3754000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-3.3896</v>
